--- a/巴赫康塔塔术语库.xlsx
+++ b/巴赫康塔塔术语库.xlsx
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>赞美 (另见: 颂赞, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美)</t>
+          <t>赞美 (另见: 颂赞, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美, 赞美)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
